--- a/static/samples/mapping_example.xlsx
+++ b/static/samples/mapping_example.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C975194-A239-497A-962A-7D886F438F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-90" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>

--- a/static/samples/mapping_example.xlsx
+++ b/static/samples/mapping_example.xlsx
@@ -1,164 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ne025\Desktop\UO_MDR\static\samples\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C975194-A239-497A-962A-7D886F438F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-90" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19310" yWindow="-90" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作表1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
-  <si>
-    <t>MDR 技術文件</t>
-  </si>
-  <si>
-    <t>CSDT 技術文件</t>
-  </si>
-  <si>
-    <t>檔案名稱/資料夾名稱/文字內容</t>
-  </si>
-  <si>
-    <t>擷取段落/操作</t>
-  </si>
-  <si>
-    <t>檔案路徑</t>
-  </si>
-  <si>
-    <t>檔案名稱</t>
-  </si>
-  <si>
-    <t>模板文件</t>
-  </si>
-  <si>
-    <t>插入段落名稱/目的資料夾名稱</t>
-  </si>
-  <si>
-    <t>Section 1_Device Description_v1.docx</t>
-  </si>
-  <si>
-    <t>1.1.1 General description\General description</t>
-  </si>
-  <si>
-    <t>輸出-USTAR II System\3. Device Description</t>
-  </si>
-  <si>
-    <t>Annex 3_Device Description_Template (draft).docx</t>
-  </si>
-  <si>
-    <t>Device Description_Template.docx</t>
-  </si>
-  <si>
-    <t>Section 2_Information Supplied by Manufacture_v1.docx</t>
-  </si>
-  <si>
-    <t>b) Primary Packaging and Secondary Packaging</t>
-  </si>
-  <si>
-    <t>1.1.1 General description\Principles of operation and mode of action</t>
-  </si>
-  <si>
-    <t>1.2.	Principle of operation and mode of action</t>
-  </si>
-  <si>
-    <t>1.6.	Key Functional Elements</t>
-  </si>
-  <si>
-    <t>a) Product Description</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.6.3 Bill of materials | index=1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>類型</t>
-  </si>
-  <si>
-    <t>Figure</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>2.1.1 Device or Product labelling | index=1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.1.1 Device or Product labelling | Figure 2.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.1.1 Device or Product labelling | Figure 1. The packaging level of the subject device.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.6.3 Bill of materials | Table 2.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.6.3 Bill of materials | Table 1. General information of the accessories.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Please refer to Annex 14_ Product CoA</t>
-  </si>
-  <si>
-    <t>Add Text</t>
-  </si>
-  <si>
-    <t>13.	 Other relevant specifications</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -184,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -268,68 +157,200 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -617,265 +638,453 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45" style="3" customWidth="1"/>
-    <col min="5" max="5" width="52.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col width="42.7109375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="86.85546875" customWidth="1" style="2" min="2" max="2"/>
+    <col width="8.42578125" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="45" customWidth="1" style="3" min="4" max="4"/>
+    <col width="52.85546875" customWidth="1" style="3" min="5" max="5"/>
+    <col width="43.140625" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
+    <col width="43.85546875" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+    <row r="1" ht="21.75" customFormat="1" customHeight="1" s="3" thickBot="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>MDR 技術文件</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="n"/>
+      <c r="C1" s="17" t="n"/>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>CSDT 技術文件</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="n"/>
+      <c r="G1" s="18" t="n"/>
+      <c r="H1" s="19" t="n"/>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
+    <row r="2" ht="21.75" customFormat="1" customHeight="1" s="3" thickBot="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>檔案名稱/資料夾名稱/文字內容</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>擷取段落/操作</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>包含標題</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>檔案路徑</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>檔案名稱</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>模板文件</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>插入段落名稱/目的資料夾名稱</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>18</v>
+    <row r="3" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Section 1_Device Description_v1.docx</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>1.1.1 General description\General description</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>a) Product Description</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>14</v>
+    <row r="4" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Section 2_Information Supplied by Manufacture_v1.docx</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2.1.1 Device or Product labelling | index=1</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>b) Primary Packaging and Secondary Packaging</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>14</v>
+    <row r="5" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Section 2_Information Supplied by Manufacture_v1.docx</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>2.1.1 Device or Product labelling | Figure 1. The packaging level of the subject device.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>b) Primary Packaging and Secondary Packaging</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>14</v>
+    <row r="6" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Section 2_Information Supplied by Manufacture_v1.docx</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>2.1.1 Device or Product labelling | Figure 2.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>b) Primary Packaging and Secondary Packaging</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>16</v>
+    <row r="7" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Section 1_Device Description_v1.docx</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1.1.1 General description\Principles of operation and mode of action</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>1.2.	Principle of operation and mode of action</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>17</v>
+    <row r="8" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Section 1_Device Description_v1.docx</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1.6.3 Bill of materials | index=1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>1.6.	Key Functional Elements</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>17</v>
+    <row r="9" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Section 1_Device Description_v1.docx</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1.6.3 Bill of materials | Table 1. General information of the accessories.</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>1.6.	Key Functional Elements</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>17</v>
+    <row r="10" ht="36.75" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Section 1_Device Description_v1.docx</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1.6.3 Bill of materials | Table 2.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>1.6.	Key Functional Elements</t>
+        </is>
       </c>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>30</v>
+    <row r="11" ht="36.75" customFormat="1" customHeight="1" s="9" thickBot="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Please refer to Annex 14_ Product CoA</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Add Text</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>輸出-USTAR II System\3. Device Description</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Annex 3_Device Description_Template (draft).docx</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Device Description_Template.docx</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>13.	 Other relevant specifications</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/static/samples/mapping_example.xlsx
+++ b/static/samples/mapping_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ne025\Downloads\範例文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9D7601-5987-4E5B-A84F-4BDBA9E08B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E25022-DC8F-4F44-98CE-DB837CA58A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping定義" sheetId="4" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="75">
   <si>
     <t>輸出-USTAR II System\3. Device Description</t>
   </si>
@@ -331,6 +331,10 @@
   </si>
   <si>
     <t>6.13.2  Sterilizing agent - 6.13.4 EO Sterilization validation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Figure Table</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1342,7 +1346,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{79AE1AA1-811C-4EDF-BA57-2FDBECE106FD}">
           <x14:formula1>
             <xm:f>欄位參數!$A$1:$A$3</xm:f>
@@ -1351,7 +1355,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1FBA8688-A804-47D7-A14A-0246BAA4CC38}">
           <x14:formula1>
-            <xm:f>欄位參數!$B$1:$B$7</xm:f>
+            <xm:f>欄位參數!$B$1:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>
@@ -1363,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD824A8-A0A2-4660-9C00-47E159F91A96}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -1405,6 +1409,11 @@
         <v>42</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
